--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:58</t>
+    <t xml:space="preserve">2026-09-10 01:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:09</t>
+    <t xml:space="preserve">2026-09-12 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:21</t>
+    <t xml:space="preserve">2026-09-23 23:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:50</t>
+    <t xml:space="preserve">2026-10-02 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:06</t>
+    <t xml:space="preserve">2026-10-05 15:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
